--- a/bzh-putevoditel-tablica.xlsx
+++ b/bzh-putevoditel-tablica.xlsx
@@ -480,7 +480,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
@@ -556,7 +556,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
@@ -626,7 +626,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G69"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -697,7 +697,11 @@
         </is>
       </c>
       <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>bzh-8-01.html</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -822,7 +826,11 @@
         </is>
       </c>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>bzh-8-06.html</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -847,7 +855,11 @@
         </is>
       </c>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>bzh-8-07.html</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1143,7 +1155,11 @@
         </is>
       </c>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>bzh-9-06.html</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1168,7 +1184,11 @@
         </is>
       </c>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>bzh-9-07.html</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1648,7 +1668,11 @@
         </is>
       </c>
       <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>bzh-10-06.html</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -1669,7 +1693,11 @@
       </c>
       <c r="E42" s="5" t="n"/>
       <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>bzh-10-07.html</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -1878,7 +1906,11 @@
         </is>
       </c>
       <c r="F51" s="5" t="n"/>
-      <c r="G51" s="5" t="n"/>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>bzh-11-06.html</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -1903,7 +1935,11 @@
         </is>
       </c>
       <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="n"/>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>bzh-11-07.html</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
